--- a/output/Pruefliste_Fachschaften.xlsx
+++ b/output/Pruefliste_Fachschaften.xlsx
@@ -564,7 +564,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>• SDG-Zuordnungen: Verbindung von Inhaltsfeldern zu den 17 Nachhaltigkeitszielen. Die Kerncurricula nennen keine SDGs.</t>
+          <t>• SDG-Zuordnungen: Verbindung von Inhaltsfeldern zu den 17 Nachhaltigkeitszielen und einem Unterziel (amtlicher Wortlaut). Die Kerncurricula nennen keine SDGs.</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -1372,7 +1372,8 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>SDG 6: Sauberes Wasser und Sanitäreinrichtungen</t>
+          <t>SDG 6: Sauberes Wasser und Sanitäreinrichtungen
+Unterziel 6.3: Bis 2030 die Wasserqualität durch Verringerung der Verschmutzung, Beendigung des Einbringens und Minimierung der Freisetzung gefährlicher Chemikalien und Stoffe, Halbierung des Anteils unbehandelten Abwassers und eine beträchtliche Steigerung der Wiederaufbereitung und gefahrlosen Wiederverwendung weltweit verbessern</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1400,7 +1401,8 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>SDG 6: Sauberes Wasser und Sanitäreinrichtungen</t>
+          <t>SDG 6: Sauberes Wasser und Sanitäreinrichtungen
+Unterziel 6.3: Bis 2030 die Wasserqualität durch Verringerung der Verschmutzung, Beendigung des Einbringens und Minimierung der Freisetzung gefährlicher Chemikalien und Stoffe, Halbierung des Anteils unbehandelten Abwassers und eine beträchtliche Steigerung der Wiederaufbereitung und gefahrlosen Wiederverwendung weltweit verbessern</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1428,7 +1430,8 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>SDG 7: Bezahlbare und saubere Energie</t>
+          <t>SDG 7: Bezahlbare und saubere Energie
+Unterziel 7.3: Bis 2030 die weltweite Steigerungsrate der Energieeffizienz verdoppeln</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1456,7 +1459,8 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>SDG 7: Bezahlbare und saubere Energie</t>
+          <t>SDG 7: Bezahlbare und saubere Energie
+Unterziel 7.2: Bis 2030 den Anteil erneuerbarer Energie am globalen Energiemix deutlich erhöhen</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -1484,7 +1488,8 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>SDG 12: Nachhaltige/r Konsum und Produktion</t>
+          <t>SDG 12: Nachhaltige/r Konsum und Produktion
+Unterziel 12.4: Bis 2020 einen umweltverträglichen Umgang mit Chemikalien und allen Abfällen während ihres gesamten Lebenszyklus in Übereinstimmung mit den vereinbarten internationalen Rahmenregelungen erreichen und ihre Freisetzung in Luft, Wasser und Boden erheblich verringern, um ihre nachteiligen Auswirkungen auf die menschliche Gesundheit und die Umwelt auf ein Mindestmaß zu beschränken</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -1512,7 +1517,8 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>SDG 12: Nachhaltige/r Konsum und Produktion</t>
+          <t>SDG 12: Nachhaltige/r Konsum und Produktion
+Unterziel 12.5: Bis 2030 das Abfallaufkommen durch Vermeidung, Verminderung, Recycling und Wiederverwendung deutlich verringern</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1553,7 +1559,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -2040,7 +2046,8 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>SDG 2: Kein Hunger</t>
+          <t>SDG 2: Kein Hunger
+Unterziel 2.2: Bis 2030 alle Formen der Fehlernährung beenden, einschließlich durch Erreichung der international vereinbarten Zielvorgaben in Bezug auf Wachstumshemmung und Auszehrung bei Kindern unter 5 Jahren bis 2025, und den Ernährungsbedürfnissen von heranwachsenden Mädchen, schwangeren und stillenden Frauen und älteren Menschen Rechnung tragen</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -2068,7 +2075,8 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>SDG 3: Gesundheit und Wohlergehen</t>
+          <t>SDG 3: Gesundheit und Wohlergehen
+Unterziel 3.3: Bis 2030 die Aids-, Tuberkulose- und Malariaepidemien und die vernachlässigten Tropenkrankheiten beseitigen und Hepatitis, durch Wasser übertragene Krankheiten und andere übertragbare Krankheiten bekämpfen</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -2096,7 +2104,8 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>SDG 3: Gesundheit und Wohlergehen</t>
+          <t>SDG 3: Gesundheit und Wohlergehen
+Unterziel 3.7: Bis 2030 den allgemeinen Zugang zu sexual- und reproduktionsmedizinischer Versorgung, einschließlich Familienplanung, Information und Aufklärung, und die Einbeziehung der reproduktiven Gesundheit in nationale Strategien und Programme gewährleisten</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -2124,7 +2133,8 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>SDG 5: Geschlechtergleichheit</t>
+          <t>SDG 5: Geschlechtergleichheit
+Unterziel 5.1: Alle Formen der Diskriminierung von Frauen und Mädchen überall auf der Welt beenden</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -2152,7 +2162,8 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>SDG 13: Maßnahmen zum Klimaschutz</t>
+          <t>SDG 13: Maßnahmen zum Klimaschutz
+Unterziel 13.3: Die Aufklärung und Sensibilisierung sowie die personellen und institutionellen Kapazitäten im Bereich der Abschwächung des Klimawandels, der Klimaanpassung, der Reduzierung der Klimaauswirkungen sowie der Frühwarnung verbessern</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2180,7 +2191,8 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>SDG 14: Leben unter Wasser</t>
+          <t>SDG 14: Leben unter Wasser
+Unterziel 14.2: Bis 2020 die Meeres- und Küstenökosysteme nachhaltig bewirtschaften und schützen, um unter anderem durch Stärkung ihrer Resilienz erhebliche nachteilige Auswirkungen zu vermeiden, und Maßnahmen zu ihrer Wiederherstellung ergreifen, damit die Meere wieder gesund und produktiv werden</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -2208,7 +2220,8 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>SDG 15: Leben an Land</t>
+          <t>SDG 15: Leben an Land
+Unterziel 15.1: Bis 2020 im Einklang mit den Verpflichtungen aus internationalen Übereinkünften die Erhaltung, Wiederherstellung und nachhaltige Nutzung der Land- und Binnensüßwasser-Ökosysteme und ihrer Dienstleistungen, insbesondere der Wälder, der Feuchtgebiete, der Berge und der Trockengebiete, gewährleisten</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -2236,7 +2249,8 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>SDG 15: Leben an Land</t>
+          <t>SDG 15: Leben an Land
+Unterziel 15.5: Umgehende und bedeutende Maßnahmen ergreifen, um die Verschlechterung der natürlichen Lebensräume zu verringern, dem Verlust der biologischen Vielfalt ein Ende zu setzen und bis 2020 die bedrohten Arten zu schützen und ihr Aussterben zu verhindern</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -2277,7 +2291,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -2700,7 +2714,8 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>SDG 1: Keine Armut</t>
+          <t>SDG 1: Keine Armut
+Unterziel 1.2: Bis 2030 den Anteil der Männer, Frauen und Kinder jeden Alters, die in Armut in all ihren Dimensionen nach der jeweiligen nationalen Definition leben, mindestens um die Hälfte senken</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -2728,7 +2743,8 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>SDG 2: Kein Hunger</t>
+          <t>SDG 2: Kein Hunger
+Unterziel 2.4: Bis 2030 die Nachhaltigkeit der Systeme der Nahrungsmittelproduktion sicherstellen und resiliente landwirtschaftliche Methoden anwenden, die die Produktivität und den Ertrag steigern, zur Erhaltung der Ökosysteme beitragen, die Anpassungsfähigkeit an Klimaänderungen, extreme Wetterereignisse, Dürren, Überschwemmungen und andere Katastrophen erhöhen und die Flächen- und Bodenqualität schrittweise verbessern</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -2756,7 +2772,8 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>SDG 6: Sauberes Wasser und Sanitäreinrichtungen</t>
+          <t>SDG 6: Sauberes Wasser und Sanitäreinrichtungen
+Unterziel 6.6: Bis 2020 wasserverbundene Ökosysteme schützen und wiederherstellen, darunter Berge, Wälder, Feuchtgebiete, Flüsse, Grundwasserleiter und Seen</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -2784,7 +2801,8 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>SDG 11: Nachhaltige Städte und Gemeinden</t>
+          <t>SDG 11: Nachhaltige Städte und Gemeinden
+Unterziel 11.6: Bis 2030 die von den Städten ausgehende Umweltbelastung pro Kopf senken, unter anderem mit besonderer Aufmerksamkeit auf der Luftqualität und der kommunalen und sonstigen Abfallbehandlung</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -2812,7 +2830,8 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>SDG 13: Maßnahmen zum Klimaschutz</t>
+          <t>SDG 13: Maßnahmen zum Klimaschutz
+Unterziel 13.1: Die Widerstandskraft und die Anpassungsfähigkeit gegenüber klimabedingten Gefahren und Naturkatastrophen in allen Ländern stärken</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -2840,7 +2859,8 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>SDG 13: Maßnahmen zum Klimaschutz</t>
+          <t>SDG 13: Maßnahmen zum Klimaschutz
+Unterziel 13.3: Die Aufklärung und Sensibilisierung sowie die personellen und institutionellen Kapazitäten im Bereich der Abschwächung des Klimawandels, der Klimaanpassung, der Reduzierung der Klimaauswirkungen sowie der Frühwarnung verbessern</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -2868,7 +2888,8 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>SDG 15: Leben an Land</t>
+          <t>SDG 15: Leben an Land
+Unterziel 15.1: Bis 2020 im Einklang mit den Verpflichtungen aus internationalen Übereinkünften die Erhaltung, Wiederherstellung und nachhaltige Nutzung der Land- und Binnensüßwasser-Ökosysteme und ihrer Dienstleistungen, insbesondere der Wälder, der Feuchtgebiete, der Berge und der Trockengebiete, gewährleisten</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -2909,7 +2930,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -3396,7 +3417,8 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>SDG 1: Keine Armut</t>
+          <t>SDG 1: Keine Armut
+Unterziel 1.3: Den nationalen Gegebenheiten entsprechende Sozialschutzsysteme und -maßnahmen für alle umsetzen, einschließlich eines Basisschutzes, und bis 2030 eine breite Versorgung der Armen und Schwachen erreichen</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -3424,7 +3446,8 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>SDG 5: Geschlechtergleichheit</t>
+          <t>SDG 5: Geschlechtergleichheit
+Unterziel 5.1: Alle Formen der Diskriminierung von Frauen und Mädchen überall auf der Welt beenden</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -3452,7 +3475,8 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>SDG 8: Menschenwürdige Arbeit und Wirtschaftswachstum</t>
+          <t>SDG 8: Menschenwürdige Arbeit und Wirtschaftswachstum
+Unterziel 8.5: Bis 2030 produktive Vollbeschäftigung und menschenwürdige Arbeit für alle Frauen und Männer, einschließlich junger Menschen und Menschen mit Behinderungen, sowie gleiches Entgelt für gleichwertige Arbeit erreichen</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -3480,7 +3504,8 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>SDG 10: Weniger Ungleichheiten</t>
+          <t>SDG 10: Weniger Ungleichheiten
+Unterziel 10.2: Bis 2030 alle Menschen unabhängig von Alter, Geschlecht, Behinderung, „Rasse“, Ethnizität, Herkunft, Religion oder wirtschaftlichem oder sonstigem Status zu Selbstbestimmung befähigen und ihre soziale, wirtschaftliche und politische Inklusion fördern</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -3508,7 +3533,8 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>SDG 11: Nachhaltige Städte und Gemeinden</t>
+          <t>SDG 11: Nachhaltige Städte und Gemeinden
+Unterziel 11.4: Die Anstrengungen zum Schutz und zur Wahrung des Weltkultur- und -naturerbes verstärken</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -3536,7 +3562,8 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>SDG 11: Nachhaltige Städte und Gemeinden</t>
+          <t>SDG 11: Nachhaltige Städte und Gemeinden
+Unterziel 11.4: Die Anstrengungen zum Schutz und zur Wahrung des Weltkultur- und -naturerbes verstärken</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -3564,7 +3591,8 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>SDG 16: Frieden, Gerechtigkeit und starke Institutionen</t>
+          <t>SDG 16: Frieden, Gerechtigkeit und starke Institutionen
+Unterziel 16.7: Dafür sorgen, dass die Entscheidungsfindung auf allen Ebenen bedarfsorientiert, inklusiv, partizipatorisch und repräsentativ ist</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -3592,7 +3620,8 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>SDG 16: Frieden, Gerechtigkeit und starke Institutionen</t>
+          <t>SDG 16: Frieden, Gerechtigkeit und starke Institutionen
+Unterziel 16.1: Alle Formen der Gewalt und die gewaltbedingte Sterblichkeit überall deutlich verringern</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -5325,7 +5354,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -5748,7 +5777,8 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>SDG 1: Keine Armut</t>
+          <t>SDG 1: Keine Armut
+Unterziel 1.2: Bis 2030 den Anteil der Männer, Frauen und Kinder jeden Alters, die in Armut in all ihren Dimensionen nach der jeweiligen nationalen Definition leben, mindestens um die Hälfte senken</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -5776,7 +5806,8 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>SDG 1: Keine Armut</t>
+          <t>SDG 1: Keine Armut
+Unterziel 1.2: Bis 2030 den Anteil der Männer, Frauen und Kinder jeden Alters, die in Armut in all ihren Dimensionen nach der jeweiligen nationalen Definition leben, mindestens um die Hälfte senken</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5804,7 +5835,8 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>SDG 5: Geschlechtergleichheit</t>
+          <t>SDG 5: Geschlechtergleichheit
+Unterziel 5.5: Die volle und wirksame Teilhabe von Frauen und ihre Chancengleichheit bei der Übernahme von Führungsrollen auf allen Ebenen der Entscheidungsfindung im politischen, wirtschaftlichen und öffentlichen Leben sicherstellen</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -5832,7 +5864,8 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>SDG 8: Menschenwürdige Arbeit und Wirtschaftswachstum</t>
+          <t>SDG 8: Menschenwürdige Arbeit und Wirtschaftswachstum
+Unterziel 8.5: Bis 2030 produktive Vollbeschäftigung und menschenwürdige Arbeit für alle Frauen und Männer, einschließlich junger Menschen und Menschen mit Behinderungen, sowie gleiches Entgelt für gleichwertige Arbeit erreichen</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -5860,7 +5893,8 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>SDG 10: Weniger Ungleichheiten</t>
+          <t>SDG 10: Weniger Ungleichheiten
+Unterziel 10.2: Bis 2030 alle Menschen unabhängig von Alter, Geschlecht, Behinderung, „Rasse“, Ethnizität, Herkunft, Religion oder wirtschaftlichem oder sonstigem Status zu Selbstbestimmung befähigen und ihre soziale, wirtschaftliche und politische Inklusion fördern</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -5888,7 +5922,8 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>SDG 12: Nachhaltige/r Konsum und Produktion</t>
+          <t>SDG 12: Nachhaltige/r Konsum und Produktion
+Unterziel 12.8: Bis 2030 sicherstellen, dass die Menschen überall über einschlägige Informationen und das Bewusstsein für nachhaltige Entwicklung und eine Lebensweise in Harmonie mit der Natur verfügen</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -5916,7 +5951,8 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>SDG 16: Frieden, Gerechtigkeit und starke Institutionen</t>
+          <t>SDG 16: Frieden, Gerechtigkeit und starke Institutionen
+Unterziel 16.7: Dafür sorgen, dass die Entscheidungsfindung auf allen Ebenen bedarfsorientiert, inklusiv, partizipatorisch und repräsentativ ist</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -5944,7 +5980,8 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>SDG 16: Frieden, Gerechtigkeit und starke Institutionen</t>
+          <t>SDG 16: Frieden, Gerechtigkeit und starke Institutionen
+Unterziel 16.3: Die Rechtsstaatlichkeit auf nationaler und internationaler Ebene fördern und den gleichberechtigten Zugang aller zur Justiz gewährleisten</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -5972,7 +6009,8 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>SDG 17: Partnerschaften zur Erreichung der Ziele</t>
+          <t>SDG 17: Partnerschaften zur Erreichung der Ziele
+Unterziel 17.16: Die Globale Partnerschaft für nachhaltige Entwicklung ausbauen, ergänzt durch Multi-Akteur-Partnerschaften zur Mobilisierung und zum Austausch von Wissen, Fachkenntnissen, Technologie und finanziellen Ressourcen, um die Erreichung der Ziele für nachhaltige Entwicklung in allen Ländern und insbesondere in den Entwicklungsländern zu unterstützen</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -6013,7 +6051,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -6436,7 +6474,8 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>SDG 1: Keine Armut</t>
+          <t>SDG 1: Keine Armut
+Unterziel 1.3: Den nationalen Gegebenheiten entsprechende Sozialschutzsysteme und -maßnahmen für alle umsetzen, einschließlich eines Basisschutzes, und bis 2030 eine breite Versorgung der Armen und Schwachen erreichen</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -6464,7 +6503,8 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>SDG 3: Gesundheit und Wohlergehen</t>
+          <t>SDG 3: Gesundheit und Wohlergehen
+Unterziel 3.4: Bis 2030 die vorzeitige Sterblichkeit aufgrund von nichtübertragbaren Krankheiten durch Prävention und Behandlung um ein Drittel senken und die psychische Gesundheit und das Wohlergehen fördern</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6492,7 +6532,8 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>SDG 4: Hochwertige Bildung</t>
+          <t>SDG 4: Hochwertige Bildung
+Unterziel 4.4: Bis 2030 die Zahl der Jugendlichen und Erwachsenen wesentlich erhöhen, die über die entsprechenden Qualifikationen einschließlich fachlicher und beruflicher Qualifikationen für eine Beschäftigung, eine menschenwürdige Arbeit und Unternehmertum verfügen</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -6520,7 +6561,8 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>SDG 8: Menschenwürdige Arbeit und Wirtschaftswachstum</t>
+          <t>SDG 8: Menschenwürdige Arbeit und Wirtschaftswachstum
+Unterziel 8.8: Die Arbeitsrechte schützen und sichere Arbeitsumgebungen für alle Erwerbstätigen, einschließlich der Arbeitsmigranten und insbesondere der Arbeitsmigrantinnen, und der Menschen in prekärer Erwerbstätigkeit, fördern</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -6548,7 +6590,8 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>SDG 8: Menschenwürdige Arbeit und Wirtschaftswachstum</t>
+          <t>SDG 8: Menschenwürdige Arbeit und Wirtschaftswachstum
+Unterziel 8.5: Bis 2030 produktive Vollbeschäftigung und menschenwürdige Arbeit für alle Frauen und Männer, einschließlich junger Menschen und Menschen mit Behinderungen, sowie gleiches Entgelt für gleichwertige Arbeit erreichen</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -6576,7 +6619,8 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>SDG 9: Industrie, Innovation und Infrastruktur</t>
+          <t>SDG 9: Industrie, Innovation und Infrastruktur
+Unterziel 9.4: Bis 2030 die Infrastruktur modernisieren und die Industrien nachrüsten, um sie nachhaltig zu machen, mit effizienterem Ressourceneinsatz und unter vermehrter Nutzung sauberer und umweltverträglicher Technologien und Industrieprozesse, wobei alle Länder Maßnahmen entsprechend ihren jeweiligen Kapazitäten ergreifen</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -6604,7 +6648,8 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>SDG 12: Nachhaltige/r Konsum und Produktion</t>
+          <t>SDG 12: Nachhaltige/r Konsum und Produktion
+Unterziel 12.8: Bis 2030 sicherstellen, dass die Menschen überall über einschlägige Informationen und das Bewusstsein für nachhaltige Entwicklung und eine Lebensweise in Harmonie mit der Natur verfügen</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -7509,7 +7554,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -7836,7 +7881,8 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>SDG 5: Geschlechtergleichheit</t>
+          <t>SDG 5: Geschlechtergleichheit
+Unterziel 5.1: Alle Formen der Diskriminierung von Frauen und Mädchen überall auf der Welt beenden</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -7864,7 +7910,8 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>SDG 10: Weniger Ungleichheiten</t>
+          <t>SDG 10: Weniger Ungleichheiten
+Unterziel 10.3: Chancengleichheit gewährleisten und Ungleichheit der Ergebnisse reduzieren, namentlich durch die Abschaffung diskriminierender Gesetze, Politiken und Praktiken und die Förderung geeigneter gesetzgeberischer, politischer und sonstiger Maßnahmen in dieser Hinsicht</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -7892,7 +7939,8 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>SDG 15: Leben an Land</t>
+          <t>SDG 15: Leben an Land
+Unterziel 15.5: Umgehende und bedeutende Maßnahmen ergreifen, um die Verschlechterung der natürlichen Lebensräume zu verringern, dem Verlust der biologischen Vielfalt ein Ende zu setzen und bis 2020 die bedrohten Arten zu schützen und ihr Aussterben zu verhindern</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -7920,7 +7968,8 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>SDG 16: Frieden, Gerechtigkeit und starke Institutionen</t>
+          <t>SDG 16: Frieden, Gerechtigkeit und starke Institutionen
+Unterziel 16.3: Die Rechtsstaatlichkeit auf nationaler und internationaler Ebene fördern und den gleichberechtigten Zugang aller zur Justiz gewährleisten</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -8745,7 +8794,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -9481,7 +9530,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -13385,7 +13434,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -14637,7 +14686,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -14804,7 +14853,8 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>SDG 10: Weniger Ungleichheiten</t>
+          <t>SDG 10: Weniger Ungleichheiten
+Unterziel 10.2: Bis 2030 alle Menschen unabhängig von Alter, Geschlecht, Behinderung, „Rasse“, Ethnizität, Herkunft, Religion oder wirtschaftlichem oder sonstigem Status zu Selbstbestimmung befähigen und ihre soziale, wirtschaftliche und politische Inklusion fördern</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -14832,7 +14882,8 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>SDG 17: Partnerschaften zur Erreichung der Ziele</t>
+          <t>SDG 17: Partnerschaften zur Erreichung der Ziele
+Unterziel 17.16: Die Globale Partnerschaft für nachhaltige Entwicklung ausbauen, ergänzt durch Multi-Akteur-Partnerschaften zur Mobilisierung und zum Austausch von Wissen, Fachkenntnissen, Technologie und finanziellen Ressourcen, um die Erreichung der Ziele für nachhaltige Entwicklung in allen Ländern und insbesondere in den Entwicklungsländern zu unterstützen</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -15233,7 +15284,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -15464,7 +15515,8 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>SDG 15: Leben an Land</t>
+          <t>SDG 15: Leben an Land
+Unterziel 15.1: Bis 2020 im Einklang mit den Verpflichtungen aus internationalen Übereinkünften die Erhaltung, Wiederherstellung und nachhaltige Nutzung der Land- und Binnensüßwasser-Ökosysteme und ihrer Dienstleistungen, insbesondere der Wälder, der Feuchtgebiete, der Berge und der Trockengebiete, gewährleisten</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -16729,7 +16781,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -17545,7 +17597,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -17840,7 +17892,8 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>SDG 3: Gesundheit und Wohlergehen</t>
+          <t>SDG 3: Gesundheit und Wohlergehen
+Unterziel 3.4: Bis 2030 die vorzeitige Sterblichkeit aufgrund von nichtübertragbaren Krankheiten durch Prävention und Behandlung um ein Drittel senken und die psychische Gesundheit und das Wohlergehen fördern</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -18493,7 +18546,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -23913,7 +23966,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -24080,7 +24133,8 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>SDG 9: Industrie, Innovation und Infrastruktur</t>
+          <t>SDG 9: Industrie, Innovation und Infrastruktur
+Unterziel 9.c: Den Zugang zur Informations- und Kommunikationstechnologie erheblich erweitern sowie anstreben, in den am wenigsten entwickelten Ländern bis 2020 einen allgemeinen und erschwinglichen Zugang zum Internet bereitzustellen</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -24108,7 +24162,8 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>SDG 9: Industrie, Innovation und Infrastruktur</t>
+          <t>SDG 9: Industrie, Innovation und Infrastruktur
+Unterziel 9.c: Den Zugang zur Informations- und Kommunikationstechnologie erheblich erweitern sowie anstreben, in den am wenigsten entwickelten Ländern bis 2020 einen allgemeinen und erschwinglichen Zugang zum Internet bereitzustellen</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -26129,7 +26184,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -26680,7 +26735,8 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>SDG 7: Bezahlbare und saubere Energie</t>
+          <t>SDG 7: Bezahlbare und saubere Energie
+Unterziel 7.3: Bis 2030 die weltweite Steigerungsrate der Energieeffizienz verdoppeln</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -26708,7 +26764,8 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>SDG 7: Bezahlbare und saubere Energie</t>
+          <t>SDG 7: Bezahlbare und saubere Energie
+Unterziel 7.2: Bis 2030 den Anteil erneuerbarer Energie am globalen Energiemix deutlich erhöhen</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -26736,7 +26793,8 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>SDG 9: Industrie, Innovation und Infrastruktur</t>
+          <t>SDG 9: Industrie, Innovation und Infrastruktur
+Unterziel 9.5: Die wissenschaftliche Forschung verbessern und die technologischen Kapazitäten der Industriesektoren in allen Ländern und insbesondere in den Entwicklungsländern ausbauen und zu diesem Zweck bis 2030 unter anderem Innovationen fördern und die Anzahl der im Bereich Forschung und Entwicklung tätigen Personen je 1 Million Menschen sowie die öffentlichen und privaten Ausgaben für Forschung und Entwicklung beträchtlich erhöhen</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -26764,7 +26822,8 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>SDG 11: Nachhaltige Städte und Gemeinden</t>
+          <t>SDG 11: Nachhaltige Städte und Gemeinden
+Unterziel 11.2: Bis 2030 den Zugang zu sicheren, bezahlbaren, zugänglichen und nachhaltigen Verkehrssystemen für alle ermöglichen und die Sicherheit im Straßenverkehr verbessern, insbesondere durch den Ausbau des öffentlichen Verkehrs, mit besonderem Augenmerk auf den Bedürfnissen von Menschen in prekären Situationen, Frauen, Kindern, Menschen mit Behinderungen und älteren Menschen</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -26792,7 +26851,8 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>SDG 13: Maßnahmen zum Klimaschutz</t>
+          <t>SDG 13: Maßnahmen zum Klimaschutz
+Unterziel 13.3: Die Aufklärung und Sensibilisierung sowie die personellen und institutionellen Kapazitäten im Bereich der Abschwächung des Klimawandels, der Klimaanpassung, der Reduzierung der Klimaauswirkungen sowie der Frühwarnung verbessern</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
